--- a/Result/profitability/9951.xlsx
+++ b/Result/profitability/9951.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-2.36</v>
       </c>
       <c r="M2" t="n">
-        <v>0.79125</v>
+        <v>0.83125</v>
       </c>
       <c r="N2" t="n">
-        <v>24.10625</v>
+        <v>24.1125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>4.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.22875</v>
+        <v>1.21</v>
       </c>
       <c r="N3" t="n">
-        <v>24.72375</v>
+        <v>24.65875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-4.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.55875</v>
+        <v>0.4725</v>
       </c>
       <c r="N4" t="n">
-        <v>25.5225</v>
+        <v>25.27625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.91</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.15125</v>
+        <v>-0.05874999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>25.9775</v>
+        <v>25.87</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.14</v>
+        <v>-0.19</v>
       </c>
       <c r="N6" t="n">
-        <v>26.96625</v>
+        <v>27.09625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.65</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2437499999999999</v>
+        <v>-0.3149999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>28.2275</v>
+        <v>28.14125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.71</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.36125</v>
+        <v>-0.4087499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>29.74</v>
+        <v>29.84</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.00874999999999998</v>
+        <v>-0.008749999999999952</v>
       </c>
       <c r="N10" t="n">
         <v>33.06125</v>
@@ -1772,7 +1772,7 @@
         <v>0.84</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.43625</v>
+        <v>-0.4362499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>34.2175</v>
@@ -1899,7 +1899,7 @@
         <v>-0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05499999999999997</v>
+        <v>0.05500000000000008</v>
       </c>
       <c r="N12" t="n">
         <v>35.2775</v>
@@ -2026,7 +2026,7 @@
         <v>0.85</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="N13" t="n">
         <v>36.67125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9951</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1570</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E75" t="n">
+        <v>371</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>95</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>101</v>
+      </c>
+      <c r="K75" t="n">
+        <v>78</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.22125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.90875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.3799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2602739726027397</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03502626970227674</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.176470588235294</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8599999999999994</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03510204081632651</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
